--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי אשרת – ירח סגול</v>
+        <v>יונתן רזאל – היינו כחולמים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a9%d7%a8%d7%aa-%d7%99%d7%a8%d7%97-%d7%a1%d7%92%d7%95%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%aa%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%94%d7%99%d7%99%d7%a0%d7%95-%d7%9b%d7%97%d7%95%d7%9c%d7%9e%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ירח סגול” שהלחין ושר קובי אשרת (מילים: שמרית אור) נכתב לפני כ-15 שנה, עוסק במזרח התיכון. זה שיר שאינו צועק, אבל נוגע בכל מה שעבר ועובר על ישראל. השיר בנוי כמו מהדורת חדשות: “יש ידיעות במזרח התיכון על אי־שקט גדול…”</v>
+        <v>יונתן רזאל לקח טקסט מקראי מוכר  מתוך ספר תהילים (שיר המעלות, תהילים קכ״ו) – והטעין אותו במשמעות אופטימית, במיוחד על רקע תקופה טעונה כמו מלחמה. הטקסט המקורי מתאר חזרה מציון (גאולה), זיכרון של בכי, הבטחה לשמחה עתידית. למעשה הוא מורכב</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי אשרת – ירח סגול</v>
+        <v>יונתן רזאל – היינו כחולמים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יונתן רזאל – היינו כחולמים</v>
+        <v>ערן צור – אדבר איתך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%aa%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%94%d7%99%d7%99%d7%a0%d7%95-%d7%9b%d7%97%d7%95%d7%9c%d7%9e%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%a8%d7%9f-%d7%a6%d7%95%d7%a8-%d7%90%d7%93%d7%91%d7%a8-%d7%90%d7%99%d7%aa%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יונתן רזאל לקח טקסט מקראי מוכר  מתוך ספר תהילים (שיר המעלות, תהילים קכ״ו) – והטעין אותו במשמעות אופטימית, במיוחד על רקע תקופה טעונה כמו מלחמה. הטקסט המקורי מתאר חזרה מציון (גאולה), זיכרון של בכי, הבטחה לשמחה עתידית. למעשה הוא מורכב</v>
+        <v>הקאבר של "אדבר איתך" בביצוע ערן צור לשיר המזוהה עם חוה אלברשטיין (מילים: רחל שפירא) הוא דוגמה נדירה לפרשנות שמצליחה לא רק לבצע שיר מחדש – אלא לשנות את נקודת המבט הרגשית שלו. במקור, מדובר בקול נשי שמדבר אל גבר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יונתן רזאל – היינו כחולמים</v>
+        <v>ערן צור – אדבר איתך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ערן צור – אדבר איתך</v>
+        <v>שיראל חדד - תרבחו ותסעדו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%a8%d7%9f-%d7%a6%d7%95%d7%a8-%d7%90%d7%93%d7%91%d7%a8-%d7%90%d7%99%d7%aa%d7%9a/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410424&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של "אדבר איתך" בביצוע ערן צור לשיר המזוהה עם חוה אלברשטיין (מילים: רחל שפירא) הוא דוגמה נדירה לפרשנות שמצליחה לא רק לבצע שיר מחדש – אלא לשנות את נקודת המבט הרגשית שלו. במקור, מדובר בקול נשי שמדבר אל גבר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,468 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ערן צור – אדבר איתך</v>
+        <v>שיראל חדד - תרבחו ותסעדו</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שיראל חדד - הבטחת לי עולם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410423&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שיראל חדד - הבטחת לי עולם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שיראל חדד - אתה לא מבין</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410422&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שיראל חדד - אתה לא מבין</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שימי תבורי - עד מתי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410421&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שימי תבורי - עד מתי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עמית שרעבי - הסטייל הישראלי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410420&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עמית שרעבי - הסטייל הישראלי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נתי גדמו - זה אני</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410419&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נתי גדמו - זה אני</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נטע ברזילי - לבד לבד לבד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410418&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נטע ברזילי - לבד לבד לבד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>נועם דדון - מחרוזת נכון להיום 2026</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410417&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>נועם דדון - מחרוזת נכון להיום 2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מקסים משעלי - משא וראח</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410416&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מקסים משעלי - משא וראח</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>מיכאל סבאג - אתה עוד יכול</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410415&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>מיכאל סבאג - אתה עוד יכול</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אריה פרננד - הבוץ הלבנוני</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410414&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אריה פרננד - הבוץ הלבנוני</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אופק יצחקי - מחרוזת שחק אותה קוסם 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410413&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אופק יצחקי - מחרוזת שחק אותה קוסם 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אבשי - קוראים לי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410412&amp;sid=35b0c9b5d56599de903ce4d9ab0f610f</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אבשי - קוראים לי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שימי תבורי – עד מתי</v>
+        <v>נועה קירל – בוחרת אותנו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%9e%d7%99-%d7%aa%d7%91%d7%95%d7%a8%d7%99-%d7%a2%d7%93-%d7%9e%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%91%d7%95%d7%97%d7%a8%d7%aa-%d7%90%d7%95%d7%aa%d7%a0%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שימי תבורי שר משאלה הכי בסיסית  עם ניסיון לנסח זעקה פשוטה וישירה נגד מציאות של מלחמות מתמשכות במוסיקה שמחברת פופ ים־תיכוני עם אסתטיקה של רוק אולד-סקול. מבחינתו אין חדש תחת השמש הים תיכונית אותה הגשה דרמטית בטון כמעט מקונן.  בשיר</v>
+        <v>ב"בוחרת אותנו" נועה קירל מציגה ניסיון לשלב בין פופ עכשווי מלוטש לבין וידוי אישי על זוגיות תחת לחץ של חיים מודרניים אינטנסיביים. זהו שיר שמכוון להיות גם המנון רומנטי וגם הצצה לחיים “מאחורי הקלעים” של כוכבת. השיר בנוי באופן הדרגתי:</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שימי תבורי – עד מתי</v>
+        <v>נועה קירל – בוחרת אותנו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה קירל – בוחרת אותנו</v>
+        <v>הסטרוקס Going Shopping</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%91%d7%95%d7%97%d7%a8%d7%aa-%d7%90%d7%95%d7%aa%d7%a0%d7%95/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a1%d7%98%d7%a8%d7%95%d7%a7%d7%a1-going-shopping/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>ב"בוחרת אותנו" נועה קירל מציגה ניסיון לשלב בין פופ עכשווי מלוטש לבין וידוי אישי על זוגיות תחת לחץ של חיים מודרניים אינטנסיביים. זהו שיר שמכוון להיות גם המנון רומנטי וגם הצצה לחיים “מאחורי הקלעים” של כוכבת. השיר בנוי באופן הדרגתי:</v>
+        <v>הסטרוקס, גיבורי האינדי מניו יורק מוציאים את את הסינגל החדש שלהם “Going Shopping” לקראתהאלבום “Reality Awaits” שצפוי לצאת בקיץ הקרוב  זה החומר החדש הראשון שלהם מאז האלבום המוערך מ־2020, “The New Abnormal”, שיר קליל וזורם שמשלב בין גיטרות לסינתיסייזרים, ומאמץ</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה קירל – בוחרת אותנו</v>
+        <v>הסטרוקס Going Shopping</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הסטרוקס Going Shopping</v>
+        <v>התקווה 6 – חופשת מלחמה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a1%d7%98%d7%a8%d7%95%d7%a7%d7%a1-going-shopping/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%97%d7%95%d7%a4%d7%a9%d7%aa-%d7%9e%d7%9c%d7%97%d7%9e%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הסטרוקס, גיבורי האינדי מניו יורק מוציאים את את הסינגל החדש שלהם “Going Shopping” לקראתהאלבום “Reality Awaits” שצפוי לצאת בקיץ הקרוב  זה החומר החדש הראשון שלהם מאז האלבום המוערך מ־2020, “The New Abnormal”, שיר קליל וזורם שמשלב בין גיטרות לסינתיסייזרים, ומאמץ</v>
+        <v>השיר "חופשת מלחמה" של התקווה 6 הוא ניסיון מובהק לתרגם מציאות מלחמתית לשפה נגישה, רגשית ופופולרית – אך דווקא הפשטות הזו היא גם מקור הכוח שלו וגם נקודת החולשה המרכזית. השיר מורכב משאלות ילדים תמימות כמו "למה יש רעמים אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הסטרוקס Going Shopping</v>
+        <v>התקווה 6 – חופשת מלחמה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>התקווה 6 – חופשת מלחמה</v>
+        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%97%d7%95%d7%a4%d7%a9%d7%aa-%d7%9e%d7%9c%d7%97%d7%9e%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410441&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חופשת מלחמה" של התקווה 6 הוא ניסיון מובהק לתרגם מציאות מלחמתית לשפה נגישה, רגשית ופופולרית – אך דווקא הפשטות הזו היא גם מקור הכוח שלו וגם נקודת החולשה המרכזית. השיר מורכב משאלות ילדים תמימות כמו "למה יש רעמים אם</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>התקווה 6 – חופשת מלחמה</v>
+        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>פבלו רוזנברג - Quiero Volver</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410440&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>פבלו רוזנברג - Quiero Volver</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שחר חדד - כמעט כרעתי ברך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410438&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שחר חדד - כמעט כרעתי ברך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עוז תירם - אני שלך</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410437&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עוז תירם - אני שלך</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נועה קירל - מצאתי פינה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410436&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נועה קירל - מצאתי פינה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>זכי צברי - החגיגה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410435&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>זכי צברי - החגיגה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלי אליאב - מחרוזת חלומות 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410434&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלי אליאב - מחרוזת חלומות 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410432&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-11</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
+        <v>רביב כנר – כיסופים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410441&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
+        <v>https://yosmusic.com/%d7%a8%d7%91%d7%99%d7%91-%d7%9b%d7%a0%d7%a8-%d7%9b%d7%99%d7%a1%d7%95%d7%a4%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "כיסופים" של רביב כנר הוא אחד הטקסטים הישירים והנוקבים ביותר שיצאו מהדור של לוחמי העשור האחרון – שיר שלא מנסה לייפות את המלחמה, אלא לשחזר את התחושה מבפנים: עייפות, בלבול, תלישות, ובעיקר געגוע. "מרוב עשן כבר אין שמיים /</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,278 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סנדי דינקל - קברי הצדיקים - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>פבלו רוזנברג - Quiero Volver</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410440&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>פבלו רוזנברג - Quiero Volver</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שחר חדד - כמעט כרעתי ברך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410438&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שחר חדד - כמעט כרעתי ברך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>עוז תירם - אני שלך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410437&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>עוז תירם - אני שלך</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נועה קירל - מצאתי פינה</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410436&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נועה קירל - מצאתי פינה</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>זכי צברי - החגיגה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410435&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>זכי צברי - החגיגה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלי אליאב - מחרוזת חלומות 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410434&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלי אליאב - מחרוזת חלומות 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410432&amp;sid=0afa63215d0cbd102cc48a858ac6b064</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-11</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אבישי עוזיאל - משהו נפתח - משהו נשרף</v>
+        <v>רביב כנר – כיסופים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רביב כנר – כיסופים</v>
+        <v>רגב קהלני - סיבה לאהבה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%91%d7%99%d7%91-%d7%9b%d7%a0%d7%a8-%d7%9b%d7%99%d7%a1%d7%95%d7%a4%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410452&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "כיסופים" של רביב כנר הוא אחד הטקסטים הישירים והנוקבים ביותר שיצאו מהדור של לוחמי העשור האחרון – שיר שלא מנסה לייפות את המלחמה, אלא לשחזר את התחושה מבפנים: עייפות, בלבול, תלישות, ובעיקר געגוע. "מרוב עשן כבר אין שמיים /</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רביב כנר – כיסופים</v>
+        <v>רגב קהלני - סיבה לאהבה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רביב כנר - כיסופים</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410451&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רביב כנר - כיסופים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>קובי גואני - הכי טוב בעולם</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410450&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>קובי גואני - הכי טוב בעולם</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410449&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עילאי גניש - אל תגידי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410448&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עילאי גניש - אל תגידי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>עדן כהן - גבגבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410447&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>עדן כהן - גבגבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410446&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מוריה כהן - געגוע</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410445&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מוריה כהן - געגוע</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירדן טרופר - בית קברות לפרפרים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410444&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירדן טרופר - בית קברות לפרפרים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410443&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רגב קהלני - סיבה לאהבה</v>
+        <v>נדב פז – שרים בכיכר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410452&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%a4%d7%96-%d7%a9%d7%a8%d7%99%d7%9d-%d7%91%d7%9b%d7%99%d7%9b%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "שרים בכיכר" של נדב פז פועל פחות כשיר זיכרון קלאסי ויותר כהתבוננות ביקורתית עדינה על עצם פעולת הזכירה. במקום להתמקד בדמויות הנופלים או בסיפורים אישיים, הוא מעביר את מרכז הכובד אל החברה – אל הטקס, אל הקולקטיב, ואל המתח</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רגב קהלני - סיבה לאהבה</v>
+        <v>נדב פז – שרים בכיכר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רביב כנר - כיסופים</v>
+        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410451&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%91%d7%99%d7%aa%d7%a8-%d7%91%d7%a0%d7%90%d7%99-%d7%96%d7%94-%d7%9c%d7%96%d7%94/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>הדואט "זה לזה" של יוני רכטר ואביתר בנאי הוא מפגש נדיר בין שלושה רבדים: שירה עברית קלאסית של אברהם שלונסקי, הלחנה רגישה ועכשווית, והקשר היסטורי טעון של שכול ומלחמה. השורות הפותחות: "הדור שלמד להשמיע / ושכח להקשיב" הן לב השיר</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,27 +507,27 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רביב כנר - כיסופים</v>
+        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קובי גואני - הכי טוב בעולם</v>
+        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410450&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%99-%d7%90%d7%91%d7%99%d7%98%d7%9c-%d7%94%d7%94%d7%a6%d7%92%d7%94-%d7%97%d7%99%d7%99%d7%91%d7%aa-%d7%9c%d7%94%d7%99%d7%9e%d7%a9%d7%9a/</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>השיר "ההצגה חייבת להימשך" של נוי אביטל הוא מונולוג תיאטרלי כמעט פרוע – זרם תודעה סרקסטי, חכם ומכאיב, שמצליח להפוך סיטואציה יומיומית (ארוחה משפחתית) לדרמה קיומית על זהות, כישלון ואמונה. אביטל מציג את עצמו כשחקן שמבצע הוראות, ומולו: אלוהים כבמאי</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -545,278 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קובי גואני - הכי טוב בעולם</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410449&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>דיויד טויב &amp; רפאל מדמון - עושה השלום - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>עילאי גניש - אל תגידי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410448&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>עילאי גניש - אל תגידי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>עדן כהן - גבגבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410447&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>עדן כהן - גבגבר</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410446&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>נועה כהן - מחרוזת זוהר אשירוב 2 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>מוריה כהן - געגוע</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410445&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>מוריה כהן - געגוע</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ירדן טרופר - בית קברות לפרפרים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410444&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ירדן טרופר - בית קברות לפרפרים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410443&amp;sid=31ee18b6f0ccb07be0d6a8d384e92647</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אביב טל &amp; שובל - געגועים של אבא ובן</v>
+        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב פז – שרים בכיכר</v>
+        <v>מיטל טרבלסי – יד מושטת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%a4%d7%96-%d7%a9%d7%a8%d7%99%d7%9d-%d7%91%d7%9b%d7%99%d7%9b%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%98%d7%9c-%d7%98%d7%a8%d7%91%d7%9c%d7%a1%d7%99-%d7%99%d7%93-%d7%9e%d7%95%d7%a9%d7%98%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "שרים בכיכר" של נדב פז פועל פחות כשיר זיכרון קלאסי ויותר כהתבוננות ביקורתית עדינה על עצם פעולת הזכירה. במקום להתמקד בדמויות הנופלים או בסיפורים אישיים, הוא מעביר את מרכז הכובד אל החברה – אל הטקס, אל הקולקטיב, ואל המתח</v>
+        <v>"יד מושטת" בביצועה של מיטל טרבלסי, למילותיו של דוד מונסונגו, הוא שיר זיכרון שבוחר במבט מצומצם ואנושי כדי להתמודד עם אחד הנושאים הגדולים והקשים ביותר – השואה. במקום לנסות להקיף את האסון כולו, הוא מתמקד במחוות קטנות, כמעט שבריריות, שמצליחות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב פז – שרים בכיכר</v>
+        <v>מיטל טרבלסי – יד מושטת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
+        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%91%d7%99%d7%aa%d7%a8-%d7%91%d7%a0%d7%90%d7%99-%d7%96%d7%94-%d7%9c%d7%96%d7%94/</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%9e%d7%9f-%d7%95%d7%90%d7%99%d7%aa%d7%99-%d7%a4%d7%a8%d7%9c-%d7%98%d7%99%d7%a4%d7%94-%d7%a2%d7%9c-%d7%94%d7%9e%d7%a6%d7%95%d7%a7/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>הדואט "זה לזה" של יוני רכטר ואביתר בנאי הוא מפגש נדיר בין שלושה רבדים: שירה עברית קלאסית של אברהם שלונסקי, הלחנה רגישה ועכשווית, והקשר היסטורי טעון של שכול ומלחמה. השורות הפותחות: "הדור שלמד להשמיע / ושכח להקשיב" הן לב השיר</v>
+        <v>"טיפה על המצוק" בביצוע הדואט של תמר אייזנמן ואיתי פרל הוא שיר שמתקיים כולו בתוך מרחב של שבר – אבל לא שבר מתפוצץ, אלא כזה שמחלחל לאט. הוא לא מתאר ישירות את אירועי השבעה באוקטובר, אלא את מה שנשאר אחריהם:</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%99-%d7%90%d7%91%d7%99%d7%98%d7%9c-%d7%94%d7%94%d7%a6%d7%92%d7%94-%d7%97%d7%99%d7%99%d7%91%d7%aa-%d7%9c%d7%94%d7%99%d7%9e%d7%a9%d7%9a/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>השיר "ההצגה חייבת להימשך" של נוי אביטל הוא מונולוג תיאטרלי כמעט פרוע – זרם תודעה סרקסטי, חכם ומכאיב, שמצליח להפוך סיטואציה יומיומית (ארוחה משפחתית) לדרמה קיומית על זהות, כישלון ואמונה. אביטל מציג את עצמו כשחקן שמבצע הוראות, ומולו: אלוהים כבמאי</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
+        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיטל טרבלסי – יד מושטת</v>
+        <v>אור חרזי - הנני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%98%d7%9c-%d7%98%d7%a8%d7%91%d7%9c%d7%a1%d7%99-%d7%99%d7%93-%d7%9e%d7%95%d7%a9%d7%98%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410476&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-14</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"יד מושטת" בביצועה של מיטל טרבלסי, למילותיו של דוד מונסונגו, הוא שיר זיכרון שבוחר במבט מצומצם ואנושי כדי להתמודד עם אחד הנושאים הגדולים והקשים ביותר – השואה. במקום לנסות להקיף את האסון כולו, הוא מתמקד במחוות קטנות, כמעט שבריריות, שמצליחות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיטל טרבלסי – יד מושטת</v>
+        <v>אור חרזי - הנני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
+        <v>שיראל חדד - תפילה מהלב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%9e%d7%9f-%d7%95%d7%90%d7%99%d7%aa%d7%99-%d7%a4%d7%a8%d7%9c-%d7%98%d7%99%d7%a4%d7%94-%d7%a2%d7%9c-%d7%94%d7%9e%d7%a6%d7%95%d7%a7/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410475&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-14</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>"טיפה על המצוק" בביצוע הדואט של תמר אייזנמן ואיתי פרל הוא שיר שמתקיים כולו בתוך מרחב של שבר – אבל לא שבר מתפוצץ, אלא כזה שמחלחל לאט. הוא לא מתאר ישירות את אירועי השבעה באוקטובר, אלא את מה שנשאר אחריהם:</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,430 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
+        <v>שיראל חדד - תפילה מהלב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עמיר בניון &amp; להקת הנוירונים - מי גילה לך את הסוד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410474&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עמיר בניון &amp; להקת הנוירונים - מי גילה לך את הסוד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>סנדי דינקל - מי שאתה - גרסה ווקאלית</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410473&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>סנדי דינקל - מי שאתה - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ניר קריגל - כטבמ</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410471&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ניר קריגל - כטבמ</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מיטל טרבלסי - יד מושטת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410470&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מיטל טרבלסי - יד מושטת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>מורן מצליח - נופלת על היין</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410469&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>מורן מצליח - נופלת על היין</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>מאיר רובין &amp; ברק מזרחי - כואב לי שאתה בוכה אחי קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410468&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>מאיר רובין &amp; ברק מזרחי - כואב לי שאתה בוכה אחי קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ליאם יהודה - הכל שתיקות</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410467&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ליאם יהודה - הכל שתיקות</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יאיר דוד - עלה - גרסת ווקאלית</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410466&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יאיר דוד - עלה - גרסת ווקאלית</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליה והב &amp; יניב בן משיח - אבינו הגדול</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410465&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליה והב &amp; יניב בן משיח - אבינו הגדול</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אלחנן ענבל - ממעמקים - גרסה ווקאלית</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410464&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אלחנן ענבל - ממעמקים - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>איציק דדיה - יצר טוב - גרסה ווקאלית</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410463&amp;sid=d20707e3871c5f5c479684e03c6d35cf</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-14</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>איציק דדיה - יצר טוב - גרסה ווקאלית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>